--- a/output/factor_reg_Lag2_adj.xlsx
+++ b/output/factor_reg_Lag2_adj.xlsx
@@ -612,58 +612,58 @@
         <v>31</v>
       </c>
       <c r="B2">
-        <v>-0.006938022896257229</v>
+        <v>0.001949513252320255</v>
       </c>
       <c r="C2">
-        <v>-1.873586552772119</v>
+        <v>0.579828838747415</v>
       </c>
       <c r="D2">
-        <v>0.06098743290424644</v>
+        <v>0.5620300478091048</v>
       </c>
       <c r="E2">
-        <v>0.003703070395115655</v>
+        <v>0.003362221955933968</v>
       </c>
       <c r="F2">
-        <v>0.7459374473852247</v>
+        <v>0.7232090134063147</v>
       </c>
       <c r="G2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H2">
-        <v>1.156479010664868</v>
+        <v>1.119947494591887</v>
       </c>
       <c r="I2">
-        <v>0.1010810397692197</v>
+        <v>0.1093058039775177</v>
       </c>
       <c r="J2">
-        <v>11.44110718790834</v>
+        <v>10.24600207709227</v>
       </c>
       <c r="K2">
-        <v>2.605391718970329E-30</v>
+        <v>1.233400866322165E-24</v>
       </c>
       <c r="L2">
-        <v>0.03199828898393316</v>
+        <v>-0.00787852590220574</v>
       </c>
       <c r="M2">
-        <v>0.1167158482204155</v>
+        <v>0.1440263198406472</v>
       </c>
       <c r="N2">
-        <v>0.274155476499687</v>
+        <v>-0.05470198718486075</v>
       </c>
       <c r="O2">
-        <v>0.7839651422618966</v>
+        <v>0.9563758861905729</v>
       </c>
       <c r="P2">
-        <v>-0.5139956860173724</v>
+        <v>-0.5662897103677053</v>
       </c>
       <c r="Q2">
-        <v>0.112027607762309</v>
+        <v>0.1088467892086692</v>
       </c>
       <c r="R2">
-        <v>-4.58811623566868</v>
+        <v>-5.202631280947355</v>
       </c>
       <c r="S2">
-        <v>4.472635985477986E-06</v>
+        <v>1.964864650935262E-07</v>
       </c>
     </row>
     <row r="3" spans="1:31">
@@ -671,70 +671,70 @@
         <v>32</v>
       </c>
       <c r="B3">
-        <v>-0.006656951771791387</v>
+        <v>0.002024477044785015</v>
       </c>
       <c r="C3">
-        <v>-1.845551569966853</v>
+        <v>0.6119180496466735</v>
       </c>
       <c r="D3">
-        <v>0.06495734402540494</v>
+        <v>0.5405919789453413</v>
       </c>
       <c r="E3">
-        <v>0.003607025606936006</v>
+        <v>0.003308412043007988</v>
       </c>
       <c r="F3">
-        <v>0.7471268389849861</v>
+        <v>0.7233066967456798</v>
       </c>
       <c r="G3">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H3">
-        <v>1.137549174353563</v>
+        <v>1.114553629633982</v>
       </c>
       <c r="I3">
-        <v>0.1097105137117151</v>
+        <v>0.1177311873147961</v>
       </c>
       <c r="J3">
-        <v>10.36864322176711</v>
+        <v>9.466936119940984</v>
       </c>
       <c r="K3">
-        <v>3.443795063336017E-25</v>
+        <v>2.881721966750483E-21</v>
       </c>
       <c r="L3">
-        <v>0.004994723071390553</v>
+        <v>-0.01547278600611886</v>
       </c>
       <c r="M3">
-        <v>0.1041151595358398</v>
+        <v>0.1341489239315808</v>
       </c>
       <c r="N3">
-        <v>0.04797306265156523</v>
+        <v>-0.115340366159108</v>
       </c>
       <c r="O3">
-        <v>0.9617377107712205</v>
+        <v>0.908175344277691</v>
       </c>
       <c r="P3">
-        <v>-0.5304196683879013</v>
+        <v>-0.5709683817465773</v>
       </c>
       <c r="Q3">
-        <v>0.1184239858108228</v>
+        <v>0.1201746686099947</v>
       </c>
       <c r="R3">
-        <v>-4.478988481566764</v>
+        <v>-4.751154202051951</v>
       </c>
       <c r="S3">
-        <v>7.499757999420067E-06</v>
+        <v>2.022588120406614E-06</v>
       </c>
       <c r="T3">
-        <v>-0.0711516462096525</v>
+        <v>-0.02021732983372096</v>
       </c>
       <c r="U3">
-        <v>0.1428759972787786</v>
+        <v>0.1408749972161244</v>
       </c>
       <c r="V3">
-        <v>-0.497995797508394</v>
+        <v>-0.1435125482395176</v>
       </c>
       <c r="W3">
-        <v>0.6184870042458284</v>
+        <v>0.8858854017680524</v>
       </c>
     </row>
     <row r="4" spans="1:31">
@@ -742,82 +742,82 @@
         <v>33</v>
       </c>
       <c r="B4">
-        <v>-0.00468160995225717</v>
+        <v>0.004173873465409345</v>
       </c>
       <c r="C4">
-        <v>-1.454609465511382</v>
+        <v>1.333273327044706</v>
       </c>
       <c r="D4">
-        <v>0.1457774090521907</v>
+        <v>0.182442123510916</v>
       </c>
       <c r="E4">
-        <v>0.003218465205443514</v>
+        <v>0.003130545988391614</v>
       </c>
       <c r="F4">
-        <v>0.7744652360490142</v>
+        <v>0.7467387083001078</v>
       </c>
       <c r="G4">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H4">
-        <v>1.140342680430448</v>
+        <v>1.132609225099942</v>
       </c>
       <c r="I4">
-        <v>0.09610269365095191</v>
+        <v>0.1046032537207468</v>
       </c>
       <c r="J4">
-        <v>11.86587635693344</v>
+        <v>10.82766725520415</v>
       </c>
       <c r="K4">
-        <v>1.780285231705874E-32</v>
+        <v>2.54557729278187E-27</v>
       </c>
       <c r="L4">
-        <v>-0.2359366739243072</v>
+        <v>-0.2801753699635898</v>
       </c>
       <c r="M4">
-        <v>0.1439702077674378</v>
+        <v>0.1552443286008365</v>
       </c>
       <c r="N4">
-        <v>-1.638788174185505</v>
+        <v>-1.804738198739456</v>
       </c>
       <c r="O4">
-        <v>0.1012573829078217</v>
+        <v>0.07111565932629997</v>
       </c>
       <c r="P4">
-        <v>-0.2392370569529701</v>
+        <v>-0.3666920504607245</v>
       </c>
       <c r="Q4">
-        <v>0.15605816055467</v>
+        <v>0.1319751049753378</v>
       </c>
       <c r="R4">
-        <v>-1.532999338853293</v>
+        <v>-2.778494099544366</v>
       </c>
       <c r="S4">
-        <v>0.1252760178106536</v>
+        <v>0.005461150512063679</v>
       </c>
       <c r="X4">
-        <v>-0.4161898312423592</v>
+        <v>-0.5018258598336532</v>
       </c>
       <c r="Y4">
-        <v>0.1914937191607897</v>
+        <v>0.2286219446855772</v>
       </c>
       <c r="Z4">
-        <v>-2.173386328628884</v>
+        <v>-2.195003023545322</v>
       </c>
       <c r="AA4">
-        <v>0.02975125292175011</v>
+        <v>0.02816338085410269</v>
       </c>
       <c r="AB4">
-        <v>-0.5399453130097218</v>
+        <v>-0.3387560047057879</v>
       </c>
       <c r="AC4">
-        <v>0.2782940592568039</v>
+        <v>0.2811890530612249</v>
       </c>
       <c r="AD4">
-        <v>-1.940197050744341</v>
+        <v>-1.204726859093012</v>
       </c>
       <c r="AE4">
-        <v>0.05235574681426605</v>
+        <v>0.2283087636656363</v>
       </c>
     </row>
     <row r="5" spans="1:31">
@@ -825,58 +825,58 @@
         <v>34</v>
       </c>
       <c r="B5">
-        <v>-0.006152542631895701</v>
+        <v>0.001668780611937434</v>
       </c>
       <c r="C5">
-        <v>-1.369209704518355</v>
+        <v>0.4018888199837337</v>
       </c>
       <c r="D5">
-        <v>0.1709337333734409</v>
+        <v>0.6877658510151818</v>
       </c>
       <c r="E5">
-        <v>0.004493499141579611</v>
+        <v>0.00415234395424331</v>
       </c>
       <c r="F5">
-        <v>0.6910191700648403</v>
+        <v>0.7074475239574129</v>
       </c>
       <c r="G5">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H5">
-        <v>1.108982125766633</v>
+        <v>1.090583344883922</v>
       </c>
       <c r="I5">
-        <v>0.1024030759618834</v>
+        <v>0.09284609696678892</v>
       </c>
       <c r="J5">
-        <v>10.82957826559252</v>
+        <v>11.74614098505427</v>
       </c>
       <c r="K5">
-        <v>2.493008612709199E-27</v>
+        <v>7.391804213344707E-32</v>
       </c>
       <c r="L5">
-        <v>0.3377428045635942</v>
+        <v>0.4166456302526144</v>
       </c>
       <c r="M5">
-        <v>0.1427651239793904</v>
+        <v>0.1161934739233042</v>
       </c>
       <c r="N5">
-        <v>2.365723470476942</v>
+        <v>3.585792008659881</v>
       </c>
       <c r="O5">
-        <v>0.01799487957729999</v>
+        <v>0.0003360567288112975</v>
       </c>
       <c r="P5">
-        <v>0.1029347403636524</v>
+        <v>0.1399137804516279</v>
       </c>
       <c r="Q5">
-        <v>0.09820359389110662</v>
+        <v>0.1008157431146715</v>
       </c>
       <c r="R5">
-        <v>1.048176917820257</v>
+        <v>1.387816784651231</v>
       </c>
       <c r="S5">
-        <v>0.2945571031122149</v>
+        <v>0.1651928424438167</v>
       </c>
     </row>
     <row r="6" spans="1:31">
@@ -884,70 +884,70 @@
         <v>35</v>
       </c>
       <c r="B6">
-        <v>-0.005698202955251603</v>
+        <v>0.002121916821871988</v>
       </c>
       <c r="C6">
-        <v>-1.258472283583951</v>
+        <v>0.5000884019484578</v>
       </c>
       <c r="D6">
-        <v>0.2082210047664799</v>
+        <v>0.6170128323059723</v>
       </c>
       <c r="E6">
-        <v>0.004527873223416514</v>
+        <v>0.004243083450055068</v>
       </c>
       <c r="F6">
-        <v>0.6940413043868716</v>
+        <v>0.710912597205327</v>
       </c>
       <c r="G6">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H6">
-        <v>1.078382839820936</v>
+        <v>1.057978864192998</v>
       </c>
       <c r="I6">
-        <v>0.09551888765141925</v>
+        <v>0.08677011994215927</v>
       </c>
       <c r="J6">
-        <v>11.2897340655423</v>
+        <v>12.1928938775035</v>
       </c>
       <c r="K6">
-        <v>1.474822161217544E-29</v>
+        <v>3.391597381002575E-34</v>
       </c>
       <c r="L6">
-        <v>0.2940926735575575</v>
+        <v>0.3707403454795632</v>
       </c>
       <c r="M6">
-        <v>0.1515240774719666</v>
+        <v>0.1207827936299178</v>
       </c>
       <c r="N6">
-        <v>1.940897304667422</v>
+        <v>3.06947980202812</v>
       </c>
       <c r="O6">
-        <v>0.05227073501634442</v>
+        <v>0.002144319046552611</v>
       </c>
       <c r="P6">
-        <v>0.07638606214699459</v>
+        <v>0.1116324549415888</v>
       </c>
       <c r="Q6">
-        <v>0.1054248114007456</v>
+        <v>0.1067188161079825</v>
       </c>
       <c r="R6">
-        <v>0.724554885439941</v>
+        <v>1.046042853667291</v>
       </c>
       <c r="S6">
-        <v>0.4687251443897836</v>
+        <v>0.2955412474814206</v>
       </c>
       <c r="T6">
-        <v>-0.115013649989977</v>
+        <v>-0.1222083877387248</v>
       </c>
       <c r="U6">
-        <v>0.0852948410074804</v>
+        <v>0.08183010205930838</v>
       </c>
       <c r="V6">
-        <v>-1.34842446074658</v>
+        <v>-1.49344049027522</v>
       </c>
       <c r="W6">
-        <v>0.1775219009688426</v>
+        <v>0.1353219207657977</v>
       </c>
     </row>
     <row r="7" spans="1:31">
@@ -955,82 +955,82 @@
         <v>36</v>
       </c>
       <c r="B7">
-        <v>-0.007039937987267962</v>
+        <v>0.0007099597665186646</v>
       </c>
       <c r="C7">
-        <v>-1.592142266387096</v>
+        <v>0.1702893219616585</v>
       </c>
       <c r="D7">
-        <v>0.1113527420095976</v>
+        <v>0.8647826084552516</v>
       </c>
       <c r="E7">
-        <v>0.004421676464404813</v>
+        <v>0.004169138489367618</v>
       </c>
       <c r="F7">
-        <v>0.695767573260214</v>
+        <v>0.7124202448440882</v>
       </c>
       <c r="G7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H7">
-        <v>1.119652458442405</v>
+        <v>1.099457334891224</v>
       </c>
       <c r="I7">
-        <v>0.09880899302566601</v>
+        <v>0.09312428599567192</v>
       </c>
       <c r="J7">
-        <v>11.3314833413146</v>
+        <v>11.80634378171043</v>
       </c>
       <c r="K7">
-        <v>9.163948936904364E-30</v>
+        <v>3.619616528411887E-32</v>
       </c>
       <c r="L7">
-        <v>0.4412043833776981</v>
+        <v>0.5259039820731121</v>
       </c>
       <c r="M7">
-        <v>0.1837410137630478</v>
+        <v>0.1606664889868363</v>
       </c>
       <c r="N7">
-        <v>2.401229721888194</v>
+        <v>3.273264919084653</v>
       </c>
       <c r="O7">
-        <v>0.01634007497186172</v>
+        <v>0.001063127835976627</v>
       </c>
       <c r="P7">
-        <v>-0.01530788816159301</v>
+        <v>0.02169956837518803</v>
       </c>
       <c r="Q7">
-        <v>0.1754730309291242</v>
+        <v>0.1327917975463583</v>
       </c>
       <c r="R7">
-        <v>-0.08723783980101225</v>
+        <v>0.1634104573937452</v>
       </c>
       <c r="S7">
-        <v>0.9304824621835064</v>
+        <v>0.8701952697450095</v>
       </c>
       <c r="X7">
-        <v>0.1484331790455247</v>
+        <v>0.1621231190798521</v>
       </c>
       <c r="Y7">
-        <v>0.1830387760335555</v>
+        <v>0.18978795406661</v>
       </c>
       <c r="Z7">
-        <v>0.8109384375380291</v>
+        <v>0.854232924724778</v>
       </c>
       <c r="AA7">
-        <v>0.4174010252413346</v>
+        <v>0.3929759436968984</v>
       </c>
       <c r="AB7">
-        <v>0.2405535959952733</v>
+        <v>0.2366335152816533</v>
       </c>
       <c r="AC7">
-        <v>0.3369934920976275</v>
+        <v>0.2664218296179025</v>
       </c>
       <c r="AD7">
-        <v>0.7138226750253815</v>
+        <v>0.8881911651947926</v>
       </c>
       <c r="AE7">
-        <v>0.4753368365313067</v>
+        <v>0.3744379303011258</v>
       </c>
     </row>
     <row r="8" spans="1:31">
@@ -1038,58 +1038,58 @@
         <v>37</v>
       </c>
       <c r="B8">
-        <v>-0.01511607159121437</v>
+        <v>-0.00688413145972812</v>
       </c>
       <c r="C8">
-        <v>-2.306404826187347</v>
+        <v>-1.409437675340408</v>
       </c>
       <c r="D8">
-        <v>0.02108802257499947</v>
+        <v>0.1587057902838328</v>
       </c>
       <c r="E8">
-        <v>0.006553954197278681</v>
+        <v>0.004884310658195981</v>
       </c>
       <c r="F8">
-        <v>0.6602930266797087</v>
+        <v>0.7025935207827381</v>
       </c>
       <c r="G8">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H8">
-        <v>1.40032201005801</v>
+        <v>1.286967018638702</v>
       </c>
       <c r="I8">
-        <v>0.1538756016754725</v>
+        <v>0.1145782427862166</v>
       </c>
       <c r="J8">
-        <v>9.100351159057197</v>
+        <v>11.23221117153945</v>
       </c>
       <c r="K8">
-        <v>9.004023005394583E-20</v>
+        <v>2.832987367755952E-29</v>
       </c>
       <c r="L8">
-        <v>0.3488688475313286</v>
+        <v>0.3853451087665207</v>
       </c>
       <c r="M8">
-        <v>0.1693233519561399</v>
+        <v>0.1949657318311628</v>
       </c>
       <c r="N8">
-        <v>2.060370548426756</v>
+        <v>1.976476097349371</v>
       </c>
       <c r="O8">
-        <v>0.0393631302217206</v>
+        <v>0.04810088032160913</v>
       </c>
       <c r="P8">
-        <v>0.3230753203118494</v>
+        <v>0.2294616754571498</v>
       </c>
       <c r="Q8">
-        <v>0.2871097486510216</v>
+        <v>0.1682022076559423</v>
       </c>
       <c r="R8">
-        <v>1.125267678404552</v>
+        <v>1.364201330380359</v>
       </c>
       <c r="S8">
-        <v>0.2604756217472455</v>
+        <v>0.1725042096084908</v>
       </c>
     </row>
     <row r="9" spans="1:31">
@@ -1097,70 +1097,70 @@
         <v>38</v>
       </c>
       <c r="B9">
-        <v>-0.01425637841018438</v>
+        <v>-0.006090422615670367</v>
       </c>
       <c r="C9">
-        <v>-2.099428035556764</v>
+        <v>-1.208157659576869</v>
       </c>
       <c r="D9">
-        <v>0.03577918545773552</v>
+        <v>0.2269866244808839</v>
       </c>
       <c r="E9">
-        <v>0.006790601139325844</v>
+        <v>0.005041082649596744</v>
       </c>
       <c r="F9">
-        <v>0.6667222714328066</v>
+        <v>0.7104007418704537</v>
       </c>
       <c r="G9">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H9">
-        <v>1.342422603899563</v>
+        <v>1.229857337017705</v>
       </c>
       <c r="I9">
-        <v>0.1597269496620918</v>
+        <v>0.1198463689578373</v>
       </c>
       <c r="J9">
-        <v>8.404484069466719</v>
+        <v>10.26194909126013</v>
       </c>
       <c r="K9">
-        <v>4.297466263892341E-17</v>
+        <v>1.045743436739025E-24</v>
       </c>
       <c r="L9">
-        <v>0.266274872349258</v>
+        <v>0.304937872013935</v>
       </c>
       <c r="M9">
-        <v>0.1711602089131978</v>
+        <v>0.1853065858461958</v>
       </c>
       <c r="N9">
-        <v>1.555705464722216</v>
+        <v>1.645585722824946</v>
       </c>
       <c r="O9">
-        <v>0.1197781465217945</v>
+        <v>0.099849080546159</v>
       </c>
       <c r="P9">
-        <v>0.2728403996093172</v>
+        <v>0.1799243891249749</v>
       </c>
       <c r="Q9">
-        <v>0.3014021491829061</v>
+        <v>0.1833071999230222</v>
       </c>
       <c r="R9">
-        <v>0.9052370739524616</v>
+        <v>0.9815456741499081</v>
       </c>
       <c r="S9">
-        <v>0.3653398049331086</v>
+        <v>0.3263237224297153</v>
       </c>
       <c r="T9">
-        <v>-0.2176267134583794</v>
+        <v>-0.2140589872089871</v>
       </c>
       <c r="U9">
-        <v>0.170539798450196</v>
+        <v>0.1507901381558046</v>
       </c>
       <c r="V9">
-        <v>-1.276105140478013</v>
+        <v>-1.419582141292355</v>
       </c>
       <c r="W9">
-        <v>0.2019183547100539</v>
+        <v>0.1557293676264296</v>
       </c>
     </row>
     <row r="10" spans="1:31">
@@ -1168,82 +1168,82 @@
         <v>39</v>
       </c>
       <c r="B10">
-        <v>-0.01339023902957744</v>
+        <v>-0.005935617153957379</v>
       </c>
       <c r="C10">
-        <v>-2.397091675947496</v>
+        <v>-1.334771499735642</v>
       </c>
       <c r="D10">
-        <v>0.01652578843616458</v>
+        <v>0.1819511440680714</v>
       </c>
       <c r="E10">
-        <v>0.00558603542948965</v>
+        <v>0.004446916311243501</v>
       </c>
       <c r="F10">
-        <v>0.6956328135858068</v>
+        <v>0.7240803401309246</v>
       </c>
       <c r="G10">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H10">
-        <v>1.300106116974827</v>
+        <v>1.209132449243363</v>
       </c>
       <c r="I10">
-        <v>0.1188955260325368</v>
+        <v>0.119096609588832</v>
       </c>
       <c r="J10">
-        <v>10.93486155752439</v>
+        <v>10.15253459706166</v>
       </c>
       <c r="K10">
-        <v>7.852574530816428E-28</v>
+        <v>3.228672667904784E-24</v>
       </c>
       <c r="L10">
-        <v>0.1827721986935153</v>
+        <v>0.3163691540974294</v>
       </c>
       <c r="M10">
-        <v>0.186624621096113</v>
+        <v>0.2225289978455366</v>
       </c>
       <c r="N10">
-        <v>0.9793573732127568</v>
+        <v>1.421698552370374</v>
       </c>
       <c r="O10">
-        <v>0.327403431320702</v>
+        <v>0.1551137805641823</v>
       </c>
       <c r="P10">
-        <v>0.7402238905155047</v>
+        <v>0.501443639947192</v>
       </c>
       <c r="Q10">
-        <v>0.4296815748993822</v>
+        <v>0.2333633681015268</v>
       </c>
       <c r="R10">
-        <v>1.722726627709931</v>
+        <v>2.148767580904277</v>
       </c>
       <c r="S10">
-        <v>0.08493797267150234</v>
+        <v>0.03165282847691349</v>
       </c>
       <c r="X10">
-        <v>-0.008537262500838819</v>
+        <v>0.1007317010204004</v>
       </c>
       <c r="Y10">
-        <v>0.2412648227357086</v>
+        <v>0.2799280028082098</v>
       </c>
       <c r="Z10">
-        <v>-0.03538544245296334</v>
+        <v>0.3598486039619833</v>
       </c>
       <c r="AA10">
-        <v>0.971772392682645</v>
+        <v>0.7189603538174064</v>
       </c>
       <c r="AB10">
-        <v>-0.9861458099648744</v>
+        <v>-0.6706856404326087</v>
       </c>
       <c r="AC10">
-        <v>0.4534389814502298</v>
+        <v>0.2784304152584916</v>
       </c>
       <c r="AD10">
-        <v>-2.17481480487384</v>
+        <v>-2.4088088214427</v>
       </c>
       <c r="AE10">
-        <v>0.02964399719858742</v>
+        <v>0.01600467930547084</v>
       </c>
     </row>
     <row r="11" spans="1:31">
@@ -1251,58 +1251,58 @@
         <v>40</v>
       </c>
       <c r="B11">
-        <v>-0.01975540411381283</v>
+        <v>-0.006879136564589864</v>
       </c>
       <c r="C11">
-        <v>-3.10663177315358</v>
+        <v>-1.109485593625037</v>
       </c>
       <c r="D11">
-        <v>0.001892319492538805</v>
+        <v>0.2672207558763494</v>
       </c>
       <c r="E11">
-        <v>0.006359107083282959</v>
+        <v>0.006200293725413386</v>
       </c>
       <c r="F11">
-        <v>0.6983383578190978</v>
+        <v>0.715890385657266</v>
       </c>
       <c r="G11">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H11">
-        <v>1.534289965965614</v>
+        <v>1.533003338619447</v>
       </c>
       <c r="I11">
-        <v>0.1721326811814685</v>
+        <v>0.1648371045161532</v>
       </c>
       <c r="J11">
-        <v>8.913414671953607</v>
+        <v>9.300110816185926</v>
       </c>
       <c r="K11">
-        <v>4.948449075154827E-19</v>
+        <v>1.402993813416024E-20</v>
       </c>
       <c r="L11">
-        <v>0.7156651805427678</v>
+        <v>0.7794819924285704</v>
       </c>
       <c r="M11">
-        <v>0.2507474727638231</v>
+        <v>0.2283821517567452</v>
       </c>
       <c r="N11">
-        <v>2.854127192806632</v>
+        <v>3.413060024317547</v>
       </c>
       <c r="O11">
-        <v>0.004315524944681954</v>
+        <v>0.0006423779178314579</v>
       </c>
       <c r="P11">
-        <v>0.3116593481353445</v>
+        <v>0.2771552397168419</v>
       </c>
       <c r="Q11">
-        <v>0.1944336995031717</v>
+        <v>0.1733865624142387</v>
       </c>
       <c r="R11">
-        <v>1.602908080912489</v>
+        <v>1.59848165773475</v>
       </c>
       <c r="S11">
-        <v>0.1089549493362643</v>
+        <v>0.1099358243242603</v>
       </c>
     </row>
     <row r="12" spans="1:31">
@@ -1310,70 +1310,70 @@
         <v>41</v>
       </c>
       <c r="B12">
-        <v>-0.01829771559596763</v>
+        <v>-0.005436185346822896</v>
       </c>
       <c r="C12">
-        <v>-2.900108000376958</v>
+        <v>-0.8883599755759043</v>
       </c>
       <c r="D12">
-        <v>0.003730341050608558</v>
+        <v>0.3743471476697974</v>
       </c>
       <c r="E12">
-        <v>0.006309322133378923</v>
+        <v>0.006119349696387139</v>
       </c>
       <c r="F12">
-        <v>0.7130702152520465</v>
+        <v>0.7325131246714254</v>
       </c>
       <c r="G12">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H12">
-        <v>1.436116220483382</v>
+        <v>1.429178762065622</v>
       </c>
       <c r="I12">
-        <v>0.1829910164408278</v>
+        <v>0.1724171219417806</v>
       </c>
       <c r="J12">
-        <v>7.848014883002557</v>
+        <v>8.289076780600748</v>
       </c>
       <c r="K12">
-        <v>4.226740632987739E-15</v>
+        <v>1.141308556161006E-16</v>
       </c>
       <c r="L12">
-        <v>0.5756195317894692</v>
+        <v>0.6333027970497038</v>
       </c>
       <c r="M12">
-        <v>0.2618180461774913</v>
+        <v>0.2318289652375722</v>
       </c>
       <c r="N12">
-        <v>2.198547961813321</v>
+        <v>2.731767345813375</v>
       </c>
       <c r="O12">
-        <v>0.02791008064235655</v>
+        <v>0.00629956082177483</v>
       </c>
       <c r="P12">
-        <v>0.2264814396456729</v>
+        <v>0.1870971684567699</v>
       </c>
       <c r="Q12">
-        <v>0.1873164774821369</v>
+        <v>0.1565219388374522</v>
       </c>
       <c r="R12">
-        <v>1.209084447294664</v>
+        <v>1.19534149555271</v>
       </c>
       <c r="S12">
-        <v>0.2266304036754233</v>
+        <v>0.2319536335024694</v>
       </c>
       <c r="T12">
-        <v>-0.3690060225959794</v>
+        <v>-0.389156147849075</v>
       </c>
       <c r="U12">
-        <v>0.1730008744362439</v>
+        <v>0.1748609920567799</v>
       </c>
       <c r="V12">
-        <v>-2.132972008369642</v>
+        <v>-2.225517213826114</v>
       </c>
       <c r="W12">
-        <v>0.03292702250110924</v>
+        <v>0.02604653684754701</v>
       </c>
     </row>
     <row r="13" spans="1:31">
@@ -1381,82 +1381,82 @@
         <v>42</v>
       </c>
       <c r="B13">
-        <v>-0.01674743044195297</v>
+        <v>-0.004590268963779958</v>
       </c>
       <c r="C13">
-        <v>-2.894373373266838</v>
+        <v>-0.7578591773091333</v>
       </c>
       <c r="D13">
-        <v>0.003799161091026227</v>
+        <v>0.4485352911414312</v>
       </c>
       <c r="E13">
-        <v>0.005786202497796746</v>
+        <v>0.006056889064902847</v>
       </c>
       <c r="F13">
-        <v>0.7237069792529196</v>
+        <v>0.7332574910754038</v>
       </c>
       <c r="G13">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H13">
-        <v>1.500575152036765</v>
+        <v>1.486932568490966</v>
       </c>
       <c r="I13">
-        <v>0.156520216517485</v>
+        <v>0.1528214478284596</v>
       </c>
       <c r="J13">
-        <v>9.587101177240791</v>
+        <v>9.72986835041657</v>
       </c>
       <c r="K13">
-        <v>9.059454379263742E-22</v>
+        <v>2.248838152513077E-22</v>
       </c>
       <c r="L13">
-        <v>0.3638804594431644</v>
+        <v>0.5327579218117788</v>
       </c>
       <c r="M13">
-        <v>0.2959270627126422</v>
+        <v>0.27173233861767</v>
       </c>
       <c r="N13">
-        <v>1.229628869045032</v>
+        <v>1.96059815523604</v>
       </c>
       <c r="O13">
-        <v>0.218836114293163</v>
+        <v>0.04992591775364229</v>
       </c>
       <c r="P13">
-        <v>0.7066815351640381</v>
+        <v>0.6152268193470638</v>
       </c>
       <c r="Q13">
-        <v>0.3201451415752118</v>
+        <v>0.2874180060745284</v>
       </c>
       <c r="R13">
-        <v>2.207378602364381</v>
+        <v>2.140529842752905</v>
       </c>
       <c r="S13">
-        <v>0.02728762000764036</v>
+        <v>0.03231197171356422</v>
       </c>
       <c r="X13">
-        <v>-0.5117903012839866</v>
+        <v>-0.2929132152550437</v>
       </c>
       <c r="Y13">
-        <v>0.414026993536227</v>
+        <v>0.3434016234982875</v>
       </c>
       <c r="Z13">
-        <v>-1.236127859473021</v>
+        <v>-0.8529756274041157</v>
       </c>
       <c r="AA13">
-        <v>0.2164110406845333</v>
+        <v>0.3936728202003015</v>
       </c>
       <c r="AB13">
-        <v>-0.7993895602766614</v>
+        <v>-0.7222288186518798</v>
       </c>
       <c r="AC13">
-        <v>0.4720175645899471</v>
+        <v>0.4419394648404957</v>
       </c>
       <c r="AD13">
-        <v>-1.693558927136769</v>
+        <v>-1.63422567141078</v>
       </c>
       <c r="AE13">
-        <v>0.09034912841892116</v>
+        <v>0.1022114740986679</v>
       </c>
     </row>
     <row r="14" spans="1:31">
@@ -1464,58 +1464,58 @@
         <v>43</v>
       </c>
       <c r="B14">
-        <v>0.0128173812175556</v>
+        <v>0.008828649816910119</v>
       </c>
       <c r="C14">
-        <v>1.790354447585504</v>
+        <v>1.246850224854496</v>
       </c>
       <c r="D14">
-        <v>0.07339694839980655</v>
+        <v>0.2124524205962377</v>
       </c>
       <c r="E14">
-        <v>0.007159130548055047</v>
+        <v>0.007080762100307915</v>
       </c>
       <c r="F14">
-        <v>0.330814291578952</v>
+        <v>0.3705084052842832</v>
       </c>
       <c r="G14">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H14">
-        <v>-0.3778109553007462</v>
+        <v>-0.41305584402756</v>
       </c>
       <c r="I14">
-        <v>0.2006901864092121</v>
+        <v>0.1835830882967938</v>
       </c>
       <c r="J14">
-        <v>-1.882558196096248</v>
+        <v>-2.249966747262601</v>
       </c>
       <c r="K14">
-        <v>0.05976026614755523</v>
+        <v>0.02445105624967209</v>
       </c>
       <c r="L14">
-        <v>-0.6836668915588348</v>
+        <v>-0.787360518330776</v>
       </c>
       <c r="M14">
-        <v>0.2593438329661026</v>
+        <v>0.2499183923364411</v>
       </c>
       <c r="N14">
-        <v>-2.636140924346533</v>
+        <v>-3.150470483464171</v>
       </c>
       <c r="O14">
-        <v>0.008385489790336082</v>
+        <v>0.001630077268379179</v>
       </c>
       <c r="P14">
-        <v>-0.8256550341527169</v>
+        <v>-0.8434449500845472</v>
       </c>
       <c r="Q14">
-        <v>0.2414600763930149</v>
+        <v>0.2206265048442937</v>
       </c>
       <c r="R14">
-        <v>-3.419426708077534</v>
+        <v>-3.822953868030521</v>
       </c>
       <c r="S14">
-        <v>0.0006275323506982968</v>
+        <v>0.0001318624571235963</v>
       </c>
     </row>
     <row r="15" spans="1:31">
@@ -1523,70 +1523,70 @@
         <v>44</v>
       </c>
       <c r="B15">
-        <v>0.01164076382417624</v>
+        <v>0.007460662391607913</v>
       </c>
       <c r="C15">
-        <v>1.619944242086085</v>
+        <v>1.06133916194796</v>
       </c>
       <c r="D15">
-        <v>0.1052442549268441</v>
+        <v>0.2885357943627485</v>
       </c>
       <c r="E15">
-        <v>0.007185904009378643</v>
+        <v>0.007029479980664024</v>
       </c>
       <c r="F15">
-        <v>0.3460970657896864</v>
+        <v>0.3935364304538336</v>
       </c>
       <c r="G15">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H15">
-        <v>-0.29856704612982</v>
+        <v>-0.31462513243164</v>
       </c>
       <c r="I15">
-        <v>0.2254286587421549</v>
+        <v>0.1995330134361755</v>
       </c>
       <c r="J15">
-        <v>-1.324441389997892</v>
+        <v>-1.57680740150942</v>
       </c>
       <c r="K15">
-        <v>0.1853564960917454</v>
+        <v>0.1148398480742187</v>
       </c>
       <c r="L15">
-        <v>-0.5706248087180785</v>
+        <v>-0.6487755830558226</v>
       </c>
       <c r="M15">
-        <v>0.2965945119691983</v>
+        <v>0.2742178241423776</v>
       </c>
       <c r="N15">
-        <v>-1.923922344110462</v>
+        <v>-2.365913248290416</v>
       </c>
       <c r="O15">
-        <v>0.0543643180310269</v>
+        <v>0.01798565829243117</v>
       </c>
       <c r="P15">
-        <v>-0.7569011080335744</v>
+        <v>-0.7580655502033474</v>
       </c>
       <c r="Q15">
-        <v>0.2418845805513838</v>
+        <v>0.2177259749033047</v>
       </c>
       <c r="R15">
-        <v>-3.129182961180054</v>
+        <v>-3.481741443757528</v>
       </c>
       <c r="S15">
-        <v>0.001752931230407917</v>
+        <v>0.0004981644508277817</v>
       </c>
       <c r="T15">
-        <v>0.2978543763863269</v>
+        <v>0.368938818015354</v>
       </c>
       <c r="U15">
-        <v>0.2356852355947844</v>
+        <v>0.2157388318346289</v>
       </c>
       <c r="V15">
-        <v>1.263780379091842</v>
+        <v>1.710117807155636</v>
       </c>
       <c r="W15">
-        <v>0.2063088655226754</v>
+        <v>0.08724409054719685</v>
       </c>
     </row>
     <row r="16" spans="1:31">
@@ -1594,82 +1594,82 @@
         <v>45</v>
       </c>
       <c r="B16">
-        <v>0.0120658204896958</v>
+        <v>0.008764142429189301</v>
       </c>
       <c r="C16">
-        <v>1.776816513436681</v>
+        <v>1.242014667968122</v>
       </c>
       <c r="D16">
-        <v>0.07559843399364166</v>
+        <v>0.2142311502385916</v>
       </c>
       <c r="E16">
-        <v>0.006790695830690104</v>
+        <v>0.007056392050125326</v>
       </c>
       <c r="F16">
-        <v>0.3342429824766717</v>
+        <v>0.3797885805498367</v>
       </c>
       <c r="G16">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H16">
-        <v>-0.3602324716063167</v>
+        <v>-0.3543233433910239</v>
       </c>
       <c r="I16">
-        <v>0.1760946173731767</v>
+        <v>0.1561847698916538</v>
       </c>
       <c r="J16">
-        <v>-2.045675654258746</v>
+        <v>-2.268616483136096</v>
       </c>
       <c r="K16">
-        <v>0.04078829258094724</v>
+        <v>0.02329165836005799</v>
       </c>
       <c r="L16">
-        <v>-0.5998171333674718</v>
+        <v>-0.8129332917753687</v>
       </c>
       <c r="M16">
-        <v>0.3508007738050918</v>
+        <v>0.3240400691421154</v>
       </c>
       <c r="N16">
-        <v>-1.709851226556119</v>
+        <v>-2.508743112935325</v>
       </c>
       <c r="O16">
-        <v>0.08729338747507202</v>
+        <v>0.01211615614513239</v>
       </c>
       <c r="P16">
-        <v>-0.9459185921170083</v>
+        <v>-0.9819188698077886</v>
       </c>
       <c r="Q16">
-        <v>0.4405775347833815</v>
+        <v>0.3569960024887134</v>
       </c>
       <c r="R16">
-        <v>-2.146996878953639</v>
+        <v>-2.750503823467414</v>
       </c>
       <c r="S16">
-        <v>0.03179353008761436</v>
+        <v>0.005950369714988713</v>
       </c>
       <c r="X16">
-        <v>0.09560047004162767</v>
+        <v>-0.2089126445786096</v>
       </c>
       <c r="Y16">
-        <v>0.4900311903523301</v>
+        <v>0.4287518644393268</v>
       </c>
       <c r="Z16">
-        <v>0.1950905818319266</v>
+        <v>-0.487257693565489</v>
       </c>
       <c r="AA16">
-        <v>0.8453220355287755</v>
+        <v>0.6260757246349735</v>
       </c>
       <c r="AB16">
-        <v>0.2594442472669394</v>
+        <v>0.3834728139460918</v>
       </c>
       <c r="AC16">
-        <v>0.681332409389645</v>
+        <v>0.6102661798194778</v>
       </c>
       <c r="AD16">
-        <v>0.3807895290044345</v>
+        <v>0.6283697616334015</v>
       </c>
       <c r="AE16">
-        <v>0.7033594296152185</v>
+        <v>0.5297617411370426</v>
       </c>
     </row>
   </sheetData>
